--- a/data/runs/2026-08-11T183516Z/tax_deed_scrub.xlsx
+++ b/data/runs/2026-08-11T183516Z/tax_deed_scrub.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 18:38 UTC</t>
+          <t>2026-08-11 18:40 UTC</t>
         </is>
       </c>
     </row>
